--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260812.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.57%</t>
+          <t>11.47%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.57%</t>
+          <t>10.75%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.24%</t>
+          <t>8.34%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>5.36%</t>
         </is>
       </c>
     </row>
@@ -726,95 +726,95 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>110,166</t>
+          <t>47,895</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.72%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>47,895</t>
+          <t>110,166</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>18,979</t>
+          <t>57,659</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>57,659</t>
+          <t>18,979</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>50,110</t>
+          <t>48,960</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>48,960</t>
+          <t>50,110</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1151,44 +1151,44 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>46,027</t>
+          <t>11,037</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>11,037</t>
+          <t>8,804</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1217,39 +1217,39 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>8,804</t>
+          <t>46,027</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>4,821</t>
+          <t>20,209</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>20,209</t>
+          <t>4,821</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1437,44 +1437,44 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>42,583</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>42,583</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>133,541,458</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
